--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_65442.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_65442.xlsx
@@ -706,7 +706,7 @@
         <v>315</v>
       </c>
       <c r="K4" t="n">
-        <v>111</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="5">

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_65442.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_65442.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lpfv</t>
+          <t>Uflicllie</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VCL</t>
+          <t>KIOULU-L</t>
         </is>
       </c>
     </row>
